--- a/recruiter_forms/003_virtual_recruitment_fair_registration_form--recruiter_forms.xlsx
+++ b/recruiter_forms/003_virtual_recruitment_fair_registration_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -804,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_type_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>Job Type 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>job_level</t>
+          <t>job_level_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Job Level</t>
+          <t>Job Level 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>job_category</t>
+          <t>job_category_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Job Category</t>
+          <t>Job Category 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>resume_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>Resume 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>career_level</t>
+          <t>career_level_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Career Level</t>
+          <t>Career Level 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>career_level</t>
+          <t>career_level_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Career Level</t>
+          <t>Career Level 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1274,7 +1274,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_level_choices</t>
+          <t>job_level_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_level_choices</t>
+          <t>job_level_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>job_category_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1410,7 +1410,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>job_category_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
